--- a/tp_systeme_croise.xlsx
+++ b/tp_systeme_croise.xlsx
@@ -688,7 +688,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>S01TP01 - Modélisation linéaire</t>
+          <t>S01TP01 - Découverte des sytèmes</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr"/>
